--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486715_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486715_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1646</v>
+        <v>10.8172</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4848</v>
+        <v>8.6092</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6798</v>
+        <v>2.208</v>
       </c>
       <c r="G2" t="n">
         <v>5.9483</v>
@@ -610,13 +610,13 @@
         <v>3.2823</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0578</v>
+        <v>0.7104</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9577</v>
+        <v>1.0821</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1001</v>
+        <v>-0.3717</v>
       </c>
       <c r="V2" t="n">
         <v>1.8415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9401</v>
+        <v>7.274</v>
       </c>
       <c r="E3" t="n">
-        <v>8.029400000000001</v>
+        <v>7.5123</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.2384</v>
       </c>
       <c r="G3" t="n">
         <v>5.0669</v>
@@ -688,13 +688,13 @@
         <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6108</v>
+        <v>0.9447</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7097</v>
+        <v>1.1926</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0989</v>
+        <v>-0.2478</v>
       </c>
       <c r="V3" t="n">
         <v>1.8415</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2676</v>
+        <v>2.3442</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9607</v>
+        <v>2.3314</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3068</v>
+        <v>0.0129</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9254</v>
+        <v>2.5581</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1311</v>
+        <v>1.3033</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2057</v>
+        <v>1.2548</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7263</v>
+        <v>2.6694</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6833</v>
+        <v>1.028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.043</v>
+        <v>1.6414</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.1113</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5522</v>
+        <v>0.2753</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2487</v>
+        <v>-0.3866</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8442</v>
+        <v>-0.3723</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1306</v>
+        <v>0.0135</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2864</v>
+        <v>-0.3859</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6565</v>
+        <v>-0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0919</v>
+        <v>2.3277</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9877</v>
+        <v>1.8944</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8959</v>
+        <v>0.4333</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3732</v>
+        <v>1.1275</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5868</v>
+        <v>-0.828</v>
       </c>
       <c r="I5" t="n">
-        <v>1.96</v>
+        <v>1.9555</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8705</v>
+        <v>2.4737</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1035</v>
+        <v>-0.1374</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7671</v>
+        <v>2.6112</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4973</v>
+        <v>-1.3462</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6903</v>
+        <v>-0.6906</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8071</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8605</v>
+        <v>-0.4137</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4966</v>
+        <v>0.1238</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3639</v>
+        <v>-0.5374</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8918</v>
+        <v>2.325</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6324</v>
+        <v>3.1463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2595</v>
+        <v>-0.8214</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1275</v>
+        <v>1.3732</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.828</v>
+        <v>-0.5868</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9555</v>
+        <v>1.96</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4737</v>
+        <v>2.8705</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1374</v>
+        <v>0.1035</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6112</v>
+        <v>2.7671</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3462</v>
+        <v>-1.4973</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6906</v>
+        <v>-0.6903</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.8071</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8495</v>
+        <v>-0.6274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1383</v>
+        <v>-0.338</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7113</v>
+        <v>-0.2894</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3209</v>
+        <v>1.8372</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6557</v>
+        <v>0.7539</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3348</v>
+        <v>1.0833</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5581</v>
+        <v>1.9254</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3033</v>
+        <v>2.1311</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2548</v>
+        <v>-0.2057</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6694</v>
+        <v>2.7263</v>
       </c>
       <c r="K7" t="n">
-        <v>1.028</v>
+        <v>2.6833</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6414</v>
+        <v>0.043</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1113</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2753</v>
+        <v>-0.5522</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3866</v>
+        <v>-0.2487</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R7" t="n">
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3957</v>
+        <v>0.4138</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6622</v>
+        <v>0.9237</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7335</v>
+        <v>-0.5099</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6138</v>
+        <v>0.6565</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0297</v>
+        <v>1.3125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3343</v>
+        <v>1.4929</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3046</v>
+        <v>-0.1805</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0877</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3034</v>
+        <v>-0.0206</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1652</v>
+        <v>0.3238</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4686</v>
+        <v>-0.3444</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2739</v>
+        <v>-0.2491</v>
       </c>
       <c r="E9" t="n">
         <v>0.2711</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.545</v>
+        <v>-0.5202</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2353</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2739</v>
+        <v>-0.2491</v>
       </c>
       <c r="E10" t="n">
         <v>-0.0145</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2594</v>
+        <v>-0.2346</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2353</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4877</v>
+        <v>-0.587</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0145</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4732</v>
+        <v>-0.5725</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6422</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1545</v>
+        <v>0.0552</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2097</v>
+        <v>0.1104</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9526</v>
+        <v>-6.1582</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.157</v>
+        <v>-3.5365</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7955</v>
+        <v>-2.6217</v>
       </c>
       <c r="G12" t="n">
         <v>-2.765</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7668</v>
+        <v>0.0276</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1932</v>
+        <v>0.4273</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5736</v>
+        <v>-0.3998</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.7185</v>
+        <v>20.9944</v>
       </c>
       <c r="E13" t="n">
-        <v>22.1701</v>
+        <v>22.44599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4517</v>
+        <v>-1.4518</v>
       </c>
       <c r="G13" t="n">
         <v>14.0339</v>
@@ -1438,10 +1438,10 @@
         <v>7.2408</v>
       </c>
       <c r="I13" t="n">
-        <v>6.793400000000001</v>
+        <v>6.793399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>25.4915</v>
+        <v>25.49150000000001</v>
       </c>
       <c r="K13" t="n">
         <v>12.7636</v>
@@ -1456,7 +1456,7 @@
         <v>-5.5227</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.9347</v>
+        <v>-5.934700000000001</v>
       </c>
       <c r="P13" t="n">
         <v>1.9308</v>
@@ -1468,13 +1468,13 @@
         <v>16.4116</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4141999999999993</v>
+        <v>0.6900999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3073</v>
+        <v>3.5832</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.8932</v>
+        <v>-2.8931</v>
       </c>
       <c r="V13" t="n">
         <v>4.3395</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6087</v>
+        <v>0.0069</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6826</v>
+        <v>-0.2337</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0739</v>
+        <v>0.2406</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5785</v>
+        <v>0.6276</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8196</v>
+        <v>0.2478</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7588</v>
+        <v>0.3798</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1987</v>
+        <v>1.8491</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1987</v>
+        <v>1.076</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.7732</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3797</v>
+        <v>-1.2215</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6209</v>
+        <v>-0.8282</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7588</v>
+        <v>-0.3934</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.3862</v>
+        <v>-2.3169</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6925</v>
+        <v>-0.4276</v>
       </c>
       <c r="T14" t="n">
-        <v>5.2675</v>
+        <v>0.2341</v>
       </c>
       <c r="U14" t="n">
-        <v>0.425</v>
+        <v>-0.6617</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8508</v>
+        <v>-0.8038</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8542</v>
+        <v>0.7284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0034</v>
+        <v>-1.5322</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6276</v>
+        <v>0.1853</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2478</v>
+        <v>-1.7656</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3798</v>
+        <v>1.9509</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8491</v>
+        <v>3.0485</v>
       </c>
       <c r="K15" t="n">
-        <v>1.076</v>
+        <v>0.442</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7732</v>
+        <v>2.6066</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2215</v>
+        <v>-2.8632</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8282</v>
+        <v>-2.2076</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3934</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3169</v>
+        <v>-1.3515</v>
       </c>
       <c r="R15" t="n">
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2853</v>
+        <v>0.1654</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3864</v>
+        <v>0.3444</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8989</v>
+        <v>-0.179</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.9268</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-1.3129</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.372</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5216</v>
+        <v>1.4765</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8936</v>
+        <v>-2.347</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1853</v>
+        <v>-2.5785</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7656</v>
+        <v>-0.8196</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9509</v>
+        <v>-1.7588</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0485</v>
+        <v>-0.1987</v>
       </c>
       <c r="K16" t="n">
-        <v>0.442</v>
+        <v>-0.1987</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6066</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8632</v>
+        <v>-2.3797</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2076</v>
+        <v>-0.6209</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.7588</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3515</v>
+        <v>-0.3862</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4028</v>
+        <v>2.2132</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1375</v>
+        <v>2.0614</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5404</v>
+        <v>0.1519</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.9268</v>
+        <v>-1.4707</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6138</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1234</v>
+        <v>-1.5798</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4648</v>
+        <v>3.8316</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6586</v>
+        <v>-5.4114</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1484</v>
+        <v>-2.8389</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6487</v>
+        <v>-1.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4996</v>
+        <v>-1.6729</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3076</v>
+        <v>2.0524</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1448</v>
+        <v>0.9038</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>1.1485</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.456</v>
+        <v>-4.8912</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7936</v>
+        <v>-2.0698</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6624</v>
+        <v>-2.8214</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8825</v>
+        <v>-0.0346</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3863</v>
+        <v>0.2546</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4962</v>
+        <v>-0.2892</v>
       </c>
       <c r="V17" t="n">
         <v>0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.0692</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3282</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5543</v>
+        <v>-1.7351</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4456</v>
+        <v>3.0662</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.9999</v>
+        <v>-4.8013</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9285</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4674</v>
+        <v>-0.6482</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8277</v>
+        <v>-0.2072</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.441</v>
       </c>
       <c r="V18" t="n">
         <v>0.6138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7312</v>
+        <v>-2.0407</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6939</v>
+        <v>-0.258</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.4251</v>
+        <v>-1.7828</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8389</v>
+        <v>-2.1484</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.166</v>
+        <v>-1.6487</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6729</v>
+        <v>-0.4996</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0524</v>
+        <v>0.3076</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9038</v>
+        <v>0.1448</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1485</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.8912</v>
+        <v>-2.456</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0698</v>
+        <v>-1.7936</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.8214</v>
+        <v>-0.6624</v>
       </c>
       <c r="P19" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.9654</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.5446</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.51</v>
-      </c>
       <c r="S19" t="n">
-        <v>-1.1859</v>
+        <v>-0.7998</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.883</v>
+        <v>-0.1794</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3029</v>
+        <v>-0.6204</v>
       </c>
       <c r="V19" t="n">
         <v>0.3282</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0692</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.741</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2303</v>
+        <v>-4.989</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3875</v>
+        <v>-2.2841</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8429</v>
+        <v>-2.705</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4251</v>
@@ -2014,13 +2014,13 @@
         <v>2.8962</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2759</v>
+        <v>-0.0346</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4959</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7718</v>
+        <v>-0.6339</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9847</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.465199999999999</v>
+        <v>-8.016999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1855</v>
+        <v>-4.8753</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2796</v>
+        <v>-3.1417</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9276</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6068</v>
+        <v>-0.1586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5243</v>
+        <v>-0.214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0825</v>
+        <v>0.0554</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.7185</v>
+        <v>-20.029</v>
       </c>
       <c r="E22" t="n">
-        <v>1.451699999999999</v>
+        <v>1.451599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.1702</v>
+        <v>-21.4808</v>
       </c>
       <c r="G22" t="n">
         <v>-14.0341</v>
@@ -2149,7 +2149,7 @@
         <v>5.5228</v>
       </c>
       <c r="L22" t="n">
-        <v>5.934799999999999</v>
+        <v>5.9348</v>
       </c>
       <c r="M22" t="n">
         <v>-25.4914</v>
@@ -2161,7 +2161,7 @@
         <v>-12.7281</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9308</v>
+        <v>-1.930800000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-16.4117</v>
@@ -2170,13 +2170,13 @@
         <v>14.4809</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4140999999999999</v>
+        <v>0.2751999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>2.8932</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.3073</v>
+        <v>-2.6179</v>
       </c>
       <c r="V22" t="n">
         <v>-4.339700000000001</v>
@@ -2185,7 +2185,7 @@
         <v>3.5125</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.8521</v>
+        <v>-7.852100000000001</v>
       </c>
     </row>
   </sheetData>
